--- a/结果/逐题分析报告.xlsx
+++ b/结果/逐题分析报告.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>平均得分</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>难度(平均得分率)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>掌握程度(平均得分率)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>区分度</t>
         </is>
@@ -469,7 +474,10 @@
         <v>0.733</v>
       </c>
       <c r="F2" t="n">
-        <v>0.217</v>
+        <v>0.733</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +501,10 @@
         <v>0.622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.457</v>
+        <v>0.622</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +528,10 @@
         <v>0.589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.327</v>
+        <v>0.589</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +555,10 @@
         <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.427</v>
+        <v>0.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +582,10 @@
         <v>0.856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.364</v>
+        <v>0.856</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +609,10 @@
         <v>0.767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.459</v>
+        <v>0.767</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="8">
@@ -613,7 +636,10 @@
         <v>0.622</v>
       </c>
       <c r="F8" t="n">
-        <v>0.475</v>
+        <v>0.622</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="9">
@@ -637,7 +663,10 @@
         <v>0.778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.454</v>
+        <v>0.778</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="10">
@@ -661,7 +690,10 @@
         <v>0.744</v>
       </c>
       <c r="F10" t="n">
-        <v>0.372</v>
+        <v>0.744</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="11">
@@ -685,7 +717,10 @@
         <v>0.722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.277</v>
+        <v>0.722</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="12">
@@ -709,7 +744,10 @@
         <v>0.633</v>
       </c>
       <c r="F12" t="n">
-        <v>0.153</v>
+        <v>0.633</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -733,7 +771,10 @@
         <v>0.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.485</v>
+        <v>0.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="14">
@@ -757,7 +798,10 @@
         <v>0.722</v>
       </c>
       <c r="F14" t="n">
-        <v>0.19</v>
+        <v>0.722</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="15">
@@ -781,7 +825,10 @@
         <v>0.889</v>
       </c>
       <c r="F15" t="n">
-        <v>0.237</v>
+        <v>0.889</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
@@ -805,7 +852,10 @@
         <v>0.844</v>
       </c>
       <c r="F16" t="n">
-        <v>0.445</v>
+        <v>0.844</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="17">
@@ -829,7 +879,10 @@
         <v>0.556</v>
       </c>
       <c r="F17" t="n">
-        <v>0.401</v>
+        <v>0.556</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="18">
@@ -853,7 +906,10 @@
         <v>0.867</v>
       </c>
       <c r="F18" t="n">
-        <v>0.286</v>
+        <v>0.867</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="19">
@@ -877,7 +933,10 @@
         <v>0.889</v>
       </c>
       <c r="F19" t="n">
-        <v>0.258</v>
+        <v>0.889</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="20">
@@ -901,7 +960,10 @@
         <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0.23</v>
+        <v>0.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -925,7 +987,10 @@
         <v>0.589</v>
       </c>
       <c r="F21" t="n">
-        <v>0.511</v>
+        <v>0.589</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -949,7 +1014,10 @@
         <v>0.889</v>
       </c>
       <c r="F22" t="n">
-        <v>0.296</v>
+        <v>0.889</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -973,7 +1041,10 @@
         <v>0.911</v>
       </c>
       <c r="F23" t="n">
-        <v>0.186</v>
+        <v>0.911</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="24">
@@ -997,7 +1068,10 @@
         <v>0.622</v>
       </c>
       <c r="F24" t="n">
-        <v>0.518</v>
+        <v>0.622</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1021,7 +1095,10 @@
         <v>0.6</v>
       </c>
       <c r="F25" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1122,10 @@
         <v>0.756</v>
       </c>
       <c r="F26" t="n">
-        <v>0.443</v>
+        <v>0.756</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="27">
@@ -1069,7 +1149,10 @@
         <v>0.8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.418</v>
+        <v>0.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="28">
@@ -1093,7 +1176,10 @@
         <v>0.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.522</v>
+        <v>0.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
@@ -1117,7 +1203,10 @@
         <v>0.6889999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.392</v>
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="30">
@@ -1141,7 +1230,10 @@
         <v>0.522</v>
       </c>
       <c r="F30" t="n">
-        <v>0.421</v>
+        <v>0.522</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1165,7 +1257,10 @@
         <v>0.656</v>
       </c>
       <c r="F31" t="n">
-        <v>0.391</v>
+        <v>0.656</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="32">
@@ -1189,7 +1284,10 @@
         <v>0.889</v>
       </c>
       <c r="F32" t="n">
-        <v>0.169</v>
+        <v>0.889</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
@@ -1213,7 +1311,10 @@
         <v>0.556</v>
       </c>
       <c r="F33" t="n">
-        <v>0.396</v>
+        <v>0.556</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1237,7 +1338,10 @@
         <v>0.522</v>
       </c>
       <c r="F34" t="n">
-        <v>0.276</v>
+        <v>0.522</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="35">
@@ -1261,7 +1365,10 @@
         <v>0.9</v>
       </c>
       <c r="F35" t="n">
-        <v>0.262</v>
+        <v>0.9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="36">
@@ -1285,7 +1392,10 @@
         <v>0.878</v>
       </c>
       <c r="F36" t="n">
-        <v>0.225</v>
+        <v>0.878</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -1309,7 +1419,10 @@
         <v>0.667</v>
       </c>
       <c r="F37" t="n">
-        <v>0.45</v>
+        <v>0.667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1333,7 +1446,10 @@
         <v>0.789</v>
       </c>
       <c r="F38" t="n">
-        <v>0.473</v>
+        <v>0.789</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="39">
@@ -1357,7 +1473,10 @@
         <v>0.756</v>
       </c>
       <c r="F39" t="n">
-        <v>0.425</v>
+        <v>0.756</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -1381,7 +1500,10 @@
         <v>0.322</v>
       </c>
       <c r="F40" t="n">
-        <v>0.439</v>
+        <v>0.322</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1405,7 +1527,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.371</v>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="42">
@@ -1423,13 +1548,16 @@
         <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.591</v>
+        <v>1.772</v>
       </c>
       <c r="E42" t="n">
         <v>0.591</v>
       </c>
       <c r="F42" t="n">
-        <v>0.607</v>
+        <v>0.591</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.487</v>
       </c>
     </row>
     <row r="43">
@@ -1447,13 +1575,16 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.794</v>
+        <v>2.383</v>
       </c>
       <c r="E43" t="n">
         <v>0.794</v>
       </c>
       <c r="F43" t="n">
-        <v>0.519</v>
+        <v>0.794</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -1471,13 +1602,16 @@
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.867</v>
+        <v>2.6</v>
       </c>
       <c r="E44" t="n">
         <v>0.867</v>
       </c>
       <c r="F44" t="n">
-        <v>0.456</v>
+        <v>0.867</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.173</v>
       </c>
     </row>
     <row r="45">
@@ -1495,13 +1629,16 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.706</v>
+        <v>2.117</v>
       </c>
       <c r="E45" t="n">
         <v>0.706</v>
       </c>
       <c r="F45" t="n">
-        <v>0.598</v>
+        <v>0.706</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.587</v>
       </c>
     </row>
     <row r="46">
@@ -1519,13 +1656,16 @@
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E46" t="n">
         <v>0.6</v>
       </c>
       <c r="F46" t="n">
-        <v>0.629</v>
+        <v>0.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.487</v>
       </c>
     </row>
     <row r="47">
@@ -1543,13 +1683,16 @@
         <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9360000000000001</v>
+        <v>4.678</v>
       </c>
       <c r="E47" t="n">
         <v>0.9360000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.416</v>
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.104</v>
       </c>
     </row>
     <row r="48">
@@ -1567,13 +1710,16 @@
         <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>0.738</v>
+        <v>3.689</v>
       </c>
       <c r="E48" t="n">
         <v>0.738</v>
       </c>
       <c r="F48" t="n">
-        <v>0.453</v>
+        <v>0.738</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.156</v>
       </c>
     </row>
     <row r="49">
@@ -1591,13 +1737,16 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>0.706</v>
+        <v>3.528</v>
       </c>
       <c r="E49" t="n">
         <v>0.706</v>
       </c>
       <c r="F49" t="n">
-        <v>0.392</v>
+        <v>0.706</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.132</v>
       </c>
     </row>
     <row r="50">
@@ -1615,13 +1764,16 @@
         <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>0.767</v>
+        <v>3.833</v>
       </c>
       <c r="E50" t="n">
         <v>0.767</v>
       </c>
       <c r="F50" t="n">
-        <v>0.593</v>
+        <v>0.767</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.232</v>
       </c>
     </row>
     <row r="51">
@@ -1639,13 +1791,16 @@
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>0.749</v>
+        <v>3.744</v>
       </c>
       <c r="E51" t="n">
         <v>0.749</v>
       </c>
       <c r="F51" t="n">
-        <v>0.604</v>
+        <v>0.749</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.228</v>
       </c>
     </row>
     <row r="52">
@@ -1663,13 +1818,16 @@
         <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>0.589</v>
+        <v>5.894</v>
       </c>
       <c r="E52" t="n">
         <v>0.589</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.589</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.188</v>
       </c>
     </row>
     <row r="53">
@@ -1687,13 +1845,16 @@
         <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>0.714</v>
+        <v>7.144</v>
       </c>
       <c r="E53" t="n">
         <v>0.714</v>
       </c>
       <c r="F53" t="n">
-        <v>0.639</v>
+        <v>0.714</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.234</v>
       </c>
     </row>
   </sheetData>
